--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-06T12:19:14+00:00</t>
+    <t>2023-05-07T12:14:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T12:14:35+00:00</t>
+    <t>2023-05-07T13:36:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-07T13:36:00+00:00</t>
+    <t>2023-05-08T07:05:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G12" t="s" s="2">
         <v>85</v>
@@ -9771,7 +9771,7 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G70" t="s" s="2">
         <v>79</v>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T07:05:14+00:00</t>
+    <t>2023-05-08T20:00:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T20:00:55+00:00</t>
+    <t>2023-05-08T21:08:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$85</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2873" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3094" uniqueCount="540">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-08T21:08:01+00:00</t>
+    <t>2023-05-11T19:02:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>Global (Whole world)</t>
+    <t>World</t>
   </si>
   <si>
     <t>Description</t>
@@ -96,7 +96,7 @@
     <t>FHIR Version</t>
   </si>
   <si>
-    <t>4.0.1</t>
+    <t>5.0.0</t>
   </si>
   <si>
     <t>Kind</t>
@@ -240,10 +240,10 @@
     <t>Mapping: Workflow Pattern</t>
   </si>
   <si>
+    <t>Mapping: FiveWs Pattern Mapping</t>
+  </si>
+  <si>
     <t>Mapping: RIM Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
     <t>Mapping: Object Implementation Information</t>
@@ -268,6 +268,9 @@
     <t>This resource allows for the definition of some activity to be performed, independent of a particular patient, practitioner, or other performance context.</t>
   </si>
   <si>
+    <t>conformance.behavior,clinical.general</t>
+  </si>
+  <si>
     <t>Act[classCode=ACT; moodCode=DEFN]</t>
   </si>
   <si>
@@ -290,7 +293,7 @@
     <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
   </si>
   <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>Within the context of the FHIR RESTful interactions, the resource has an id except for cases like the create and conditional update. Otherwise, the use of the resouce id depends on the given use case.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -329,7 +332,7 @@
     <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
   </si>
   <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of its narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -351,13 +354,13 @@
     <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
-    <t>preferred</t>
-  </si>
-  <si>
-    <t>A human language.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>IETF language tag for a human language</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/all-languages|5.0.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -380,10 +383,14 @@
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
   </si>
   <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>Contained resources do not have a narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dom-6
+</t>
   </si>
   <si>
     <t>Act.text?</t>
@@ -403,13 +410,17 @@
     <t>Contained, inline Resources</t>
   </si>
   <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, nor can they have their own independent transaction scope. This is allowed to be a Parameters resource if and only if it is referenced by a resource that provides context/meaning.</t>
+  </si>
+  <si>
+    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags in their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
+  </si>
+  <si>
+    <t>dom-2
+dom-4dom-3dom-5</t>
   </si>
   <si>
     <t>N/A</t>
@@ -458,550 +469,622 @@
     <t>The user index for the person who reviewed the viral load result.</t>
   </si>
   <si>
+    <t>ActivityDefinition.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R5/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.url</t>
+  </si>
+  <si>
+    <t>Canonical identifier for this activity definition, represented as a URI (globally unique)</t>
+  </si>
+  <si>
+    <t>An absolute URI that is used to identify this activity definition when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which an authoritative instance of this activity definition is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the activity definition is stored on different servers.</t>
+  </si>
+  <si>
+    <t>Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
+The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R5/resource.html#versions). 
+In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R5/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
+  </si>
+  <si>
+    <t>Allows the activity definition to be referenced by a single globally unique identifier.</t>
+  </si>
+  <si>
+    <t>cnl-1:URL should not contain | or # - these characters make processing canonical references problematic {exists() implies matches('^[^|# ]+$')}
+ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}</t>
+  </si>
+  <si>
+    <t>Definition.url</t>
+  </si>
+  <si>
+    <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>.identifier[scope=BUSN;reliability=ISS]</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Additional identifier for the activity definition</t>
+  </si>
+  <si>
+    <t>A formal identifier that is used to identify this activity definition when it is represented in other formats, or referenced in a specification, model, design or an instance.</t>
+  </si>
+  <si>
+    <t>Typically, this is used for identifiers that can go in an HL7 V3 II (instance identifier) data type, and can then identify this activity definition outside of FHIR, where it is not possible to use the logical URI.</t>
+  </si>
+  <si>
+    <t>Allows externally provided and/or usable business identifiers to be easily associated with the module.</t>
+  </si>
+  <si>
+    <t>Definition.identifier</t>
+  </si>
+  <si>
+    <t>.identifier</t>
+  </si>
+  <si>
+    <t>no-gen-base</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Business version of the activity definition</t>
+  </si>
+  <si>
+    <t>The identifier that is used to identify this version of the activity definition when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the activity definition author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence. To provide a version consistent with the Decision Support Service specification, use the format Major.Minor.Revision (e.g. 1.0.0). For more information on versioning knowledge assets, refer to the Decision Support Service specification. Note that a version is required for non-experimental active assets.</t>
+  </si>
+  <si>
+    <t>There may be different activity definition instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the activity definition with the format [url]|[version]. The version SHOULD NOT contain a '#' - see [Business Version](http://hl7.org/fhir/R5/resource.html#bv-format).</t>
+  </si>
+  <si>
+    <t>Definition.version</t>
+  </si>
+  <si>
+    <t>FiveWs.version</t>
+  </si>
+  <si>
+    <t>N/A (to add?)</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.versionAlgorithm[x]</t>
+  </si>
+  <si>
+    <t>string
+Coding</t>
+  </si>
+  <si>
+    <t>How to compare versions</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to compare versions to determine which is more current.</t>
+  </si>
+  <si>
+    <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/version-algorithm</t>
+  </si>
+  <si>
+    <t>Definition.versionAlgorithm</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.name</t>
+  </si>
+  <si>
+    <t>Name for this activity definition (computer friendly)</t>
+  </si>
+  <si>
+    <t>A natural language name identifying the activity definition. This name should be usable as an identifier for the module by machine processing applications such as code generation.</t>
+  </si>
+  <si>
+    <t>The name is not expected to be globally unique. The name should be a simple alphanumeric type name to ensure that it is machine-processing friendly.</t>
+  </si>
+  <si>
+    <t>Support human navigation and code generation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cnl-0
+</t>
+  </si>
+  <si>
+    <t>Definition.name</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.title</t>
+  </si>
+  <si>
+    <t>Name for this activity definition (human friendly)</t>
+  </si>
+  <si>
+    <t>A short, descriptive, user-friendly title for the activity definition.</t>
+  </si>
+  <si>
+    <t>This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
+  </si>
+  <si>
+    <t>Definition.title</t>
+  </si>
+  <si>
+    <t>.title</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.subtitle</t>
+  </si>
+  <si>
+    <t>Subordinate title of the activity definition</t>
+  </si>
+  <si>
+    <t>An explanatory or alternate title for the activity definition giving additional information about its content.</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.status</t>
+  </si>
+  <si>
+    <t>draft | active | retired | unknown</t>
+  </si>
+  <si>
+    <t>The status of this activity definition. Enables tracking the life-cycle of the content.</t>
+  </si>
+  <si>
+    <t>Allows filtering of activity definitions that are appropriate for use versus not.
+See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
+  </si>
+  <si>
+    <t>The lifecycle status of an artifact.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/publication-status|5.0.0</t>
+  </si>
+  <si>
+    <t>Definition.status {different ValueSet}</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.experimental</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>For testing purposes, not real usage</t>
+  </si>
+  <si>
+    <t>A Boolean value to indicate that this activity definition is authored for testing purposes (or education/evaluation/marketing) and is not intended to be used for genuine usage.</t>
+  </si>
+  <si>
+    <t>Allows filtering of activity definitions that are appropriate for use versus not.</t>
+  </si>
+  <si>
+    <t>Enables experimental content to be developed following the same lifecycle that would be used for a production-level activity definition.</t>
+  </si>
+  <si>
+    <t>If absent, this resource is treated as though it is not experimental.</t>
+  </si>
+  <si>
+    <t>Definition.experimental</t>
+  </si>
+  <si>
+    <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.subject[x]</t>
+  </si>
+  <si>
+    <t>CodeableConcept
+Reference(Group|MedicinalProductDefinition|SubstanceDefinition|AdministrableProductDefinition|ManufacturedItemDefinition|PackagedProductDefinition)canonical(EvidenceVariable)</t>
+  </si>
+  <si>
+    <t>Type of individual the activity definition is intended for</t>
+  </si>
+  <si>
+    <t>A code, group definition, or canonical reference that describes  or identifies the intended subject of the activity being defined.  Canonical references are allowed to support the definition of protocols for drug and substance quality specifications, and is allowed to reference a MedicinalProductDefinition, SubstanceDefinition, AdministrableProductDefinition, ManufacturedItemDefinition, or PackagedProductDefinition resource.</t>
+  </si>
+  <si>
+    <t>Note that the choice of canonical for the subject element was introduced in R4B to support pharmaceutical quality use cases. To ensure as much backwards-compatibility as possible, it is recommended to only use the new canonical type with these use cases.</t>
+  </si>
+  <si>
+    <t>Patient</t>
+  </si>
+  <si>
+    <t>The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/participant-resource-types</t>
+  </si>
+  <si>
+    <t>Definition.subject</t>
+  </si>
+  <si>
+    <t>N/A (to add?) { only applies for subject Patient? }</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revision Date
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date last changed</t>
+  </si>
+  <si>
+    <t>The date  (and optionally time) when the activity definition was last significantly changed. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the activity definition changes.</t>
+  </si>
+  <si>
+    <t>The date is often not tracked until the resource is published, but may be present on draft content. Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the activity definition. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.
+See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
+  </si>
+  <si>
+    <t>Definition.date</t>
+  </si>
+  <si>
+    <t>FiveWs.recorded</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].time</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.publisher</t>
+  </si>
+  <si>
+    <t>Name of the publisher/steward (organization or individual)</t>
+  </si>
+  <si>
+    <t>The name of the organization or individual responsible for the release and ongoing maintenance of the activity definition.</t>
+  </si>
+  <si>
+    <t>Usually an organization but may be an individual. The publisher (or steward) of the activity definition is the organization or individual primarily responsible for the maintenance and upkeep of the activity definition. This is not necessarily the same individual or organization that developed and initially authored the content. The publisher is the primary point of contact for questions or issues with the activity definition. This item SHOULD be populated unless the information is available from context.</t>
+  </si>
+  <si>
+    <t>Helps establish the "authority/credibility" of the activity definition.  May also allow for contact.</t>
+  </si>
+  <si>
+    <t>Definition.publisher {as string instead of CodeableConcept}</t>
+  </si>
+  <si>
+    <t>FiveWs.witness</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT].role</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ContactDetail
+</t>
+  </si>
+  <si>
+    <t>Contact details for the publisher</t>
+  </si>
+  <si>
+    <t>Contact details to assist a user in finding and communicating with the publisher.</t>
+  </si>
+  <si>
+    <t>May be a web site, an email address, a telephone number, etc.
+See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
+  </si>
+  <si>
+    <t>Definition.contact</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=CALLBCK].role</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">markdown
+</t>
+  </si>
+  <si>
+    <t>Natural language description of the activity definition</t>
+  </si>
+  <si>
+    <t>A free text natural language description of the activity definition from a consumer's perspective.</t>
+  </si>
+  <si>
+    <t>This description can be used to capture details such as comments about misuse, instructions for clinical use and interpretation, literature references, examples from the paper world, etc. It is not a rendering of the activity definition as conveyed in the 'text' field of the resource itself. This item SHOULD be populated unless the information is available from context (e.g. the language of the activity definition is presumed to be the predominant language in the place the activity definition was created).</t>
+  </si>
+  <si>
+    <t>Definition.description</t>
+  </si>
+  <si>
+    <t>.text</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.useContext</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UsageContext
+</t>
+  </si>
+  <si>
+    <t>The context that the content is intended to support</t>
+  </si>
+  <si>
+    <t>The content was developed with a focus and intent of supporting the contexts that are listed. These contexts may be general categories (gender, age, ...) or may be references to specific programs (insurance plans, studies, ...) and may be used to assist with indexing and searching for appropriate activity definition instances.</t>
+  </si>
+  <si>
+    <t>When multiple useContexts are specified, there is no expectation that all or any of the contexts apply.</t>
+  </si>
+  <si>
+    <t>Assist in searching for appropriate content.</t>
+  </si>
+  <si>
+    <t>Definition.useContext</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.jurisdiction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Intended jurisdiction for activity definition (if applicable)</t>
+  </si>
+  <si>
+    <t>A legal or geographic region in which the activity definition is intended to be used.</t>
+  </si>
+  <si>
+    <t>It may be possible for the activity definition to be used in jurisdictions other than those for which it was originally designed or intended.
+DEPRECATION NOTE: For consistency, implementations are encouraged to migrate to using the new 'jurisdiction' code in the useContext element.  (I.e. useContext.code indicating http://terminology.hl7.org/CodeSystem/usage-context-type#jurisdiction and useContext.valueCodeableConcept indicating the jurisdiction.)</t>
+  </si>
+  <si>
+    <t>Countries and regions within which this artifact is targeted for use.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+  </si>
+  <si>
+    <t>Definition.jurisdiction</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.purpose</t>
+  </si>
+  <si>
+    <t>Why this activity definition is defined</t>
+  </si>
+  <si>
+    <t>Explanation of why this activity definition is needed and why it has been designed as it has.</t>
+  </si>
+  <si>
+    <t>This element does not describe the usage of the activity definition. Instead, it provides traceability of ''why'' the resource is either needed or ''why'' it is defined as it is.  This may be used to point to source materials or specifications that drove the structure of this activity definition.</t>
+  </si>
+  <si>
+    <t>Definition.purpose</t>
+  </si>
+  <si>
+    <t>FiveWs.why[x]</t>
+  </si>
+  <si>
+    <t>.reasonCode.text</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.usage</t>
+  </si>
+  <si>
+    <t>Describes the clinical usage of the activity definition</t>
+  </si>
+  <si>
+    <t>A detailed description of how the activity definition is used from a clinical perspective.</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.copyright</t>
+  </si>
+  <si>
+    <t>License
+Restrictions</t>
+  </si>
+  <si>
+    <t>Use and/or publishing restrictions</t>
+  </si>
+  <si>
+    <t>A copyright statement relating to the activity definition and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the activity definition.</t>
+  </si>
+  <si>
+    <t>The short copyright declaration (e.g. (c) '2015+ xyz organization' should be sent in the copyrightLabel element.</t>
+  </si>
+  <si>
+    <t>Consumers must be able to determine any legal restrictions on the use of the activity definition and/or its content.</t>
+  </si>
+  <si>
+    <t>Definition.copyright</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.copyrightLabel</t>
+  </si>
+  <si>
+    <t>Copyright holder and year(s)</t>
+  </si>
+  <si>
+    <t>A short string (&lt;50 characters), suitable for inclusion in a page footer that identifies the copyright holder, effective period, and optionally whether rights are resctricted. (e.g. 'All rights reserved', 'Some rights reserved').</t>
+  </si>
+  <si>
+    <t>The (c) symbol should NOT be included in this string. It will be added by software when rendering the notation. Full details about licensing, restrictions, warrantees, etc. goes in the more general 'copyright' element.</t>
+  </si>
+  <si>
+    <t>Defines the content expected to be rendered in all representations of the artifact.</t>
+  </si>
+  <si>
+    <t>Definition.copyrightLabel</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.approvalDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">date
+</t>
+  </si>
+  <si>
+    <t>When the activity definition was approved by publisher</t>
+  </si>
+  <si>
+    <t>The date on which the resource content was approved by the publisher. Approval happens once when the content is officially approved for usage.</t>
+  </si>
+  <si>
+    <t>The 'date' element may be more recent than the approval date because of minor changes or editorial corrections.
+See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
+  </si>
+  <si>
+    <t>Definition.approvalDate</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="SUBJ"].act[classCode=CACT;moodCode=EVN;code="approval"].effectiveTime</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.lastReviewDate</t>
+  </si>
+  <si>
+    <t>When the activity definition was last reviewed by the publisher</t>
+  </si>
+  <si>
+    <t>The date on which the resource content was last reviewed. Review happens periodically after approval but does not change the original approval date.</t>
+  </si>
+  <si>
+    <t>If specified, this date follows the original approval date.
+See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
+  </si>
+  <si>
+    <t>Gives a sense of how "current" the content is.  Resources that have not been reviewed in a long time may have a risk of being less appropriate/relevant.</t>
+  </si>
+  <si>
+    <t>Definition.lastReviewDate</t>
+  </si>
+  <si>
+    <t>.outboundRelationship[typeCode="SUBJ"; subsetCode="RECENT"].act[classCode=CACT;moodCode=EVN;code="review"].effectiveTime</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.effectivePeriod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>When the activity definition is expected to be used</t>
+  </si>
+  <si>
+    <t>The period during which the activity definition content was or is planned to be in active use.</t>
+  </si>
+  <si>
+    <t>The effective period for an activity definition  determines when the content is applicable for usage and is independent of publication and review dates. For example, a activity intended to be used for the year 2016 might be published in 2015.
+See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
+  </si>
+  <si>
+    <t>Allows establishing a transition before a resource comes into effect and also allows for a sunsetting  process when new versions of the activity definition are or are expected to be used instead.</t>
+  </si>
+  <si>
+    <t>Definition.effectivePeriod</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.topic</t>
+  </si>
+  <si>
+    <t>E.g. Education, Treatment, Assessment, etc</t>
+  </si>
+  <si>
+    <t>Descriptive topics related to the content of the activity. Topics provide a high-level categorization of the activity that can be useful for filtering and searching.</t>
+  </si>
+  <si>
+    <t>DEPRECATION NOTE: For consistency, implementations are encouraged to migrate to using the new 'topic' code in the useContext element.  (I.e. useContext.code indicating http://terminology.hl7.org/CodeSystem/usage-context-type#topic and useContext.valueCodeableConcept indicating the topic)</t>
+  </si>
+  <si>
+    <t>Repositories must be able to determine how to categorize the activity definition so that it can be found by topical searches.</t>
+  </si>
+  <si>
+    <t>example</t>
+  </si>
+  <si>
+    <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.author</t>
+  </si>
+  <si>
+    <t>Who authored the content</t>
+  </si>
+  <si>
+    <t>An individiual or organization primarily involved in the creation and maintenance of the content.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT]</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.editor</t>
+  </si>
+  <si>
+    <t>Who edited the content</t>
+  </si>
+  <si>
+    <t>An individual or organization primarily responsible for internal coherence of the content.</t>
+  </si>
+  <si>
+    <t>.participation[typeCode=AUT] { not a great match, but there does not appear to be an editor concept in V3 participation }</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.editor.id</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>ActivityDefinition.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.url</t>
-  </si>
-  <si>
-    <t>Canonical identifier for this activity definition, represented as a URI (globally unique)</t>
-  </si>
-  <si>
-    <t>An absolute URI that is used to identify this activity definition when it is referenced in a specification, model, design or an instance; also called its canonical identifier. This SHOULD be globally unique and SHOULD be a literal address at which at which an authoritative instance of this activity definition is (or will be) published. This URL can be the target of a canonical reference. It SHALL remain the same when the activity definition is stored on different servers.</t>
-  </si>
-  <si>
-    <t>Can be a urn:uuid: or a urn:oid: but real http: addresses are preferred.  Multiple instances may share the same URL if they have a distinct version.
-The determination of when to create a new version of a resource (same url, new version) vs. defining a new artifact is up to the author.  Considerations for making this decision are found in [Technical and Business Versions](http://hl7.org/fhir/R4/resource.html#versions). 
-In some cases, the resource can no longer be found at the stated url, but the url itself cannot change. Implementations can use the [meta.source](http://hl7.org/fhir/R4/resource.html#meta) element to indicate where the current master source of the resource can be found.</t>
-  </si>
-  <si>
-    <t>Allows the activity definition to be referenced by a single globally unique identifier.</t>
-  </si>
-  <si>
-    <t>Definition.url</t>
-  </si>
-  <si>
-    <t>.identifier[scope=BUSN;reliability=ISS]</t>
-  </si>
-  <si>
-    <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Additional identifier for the activity definition</t>
-  </si>
-  <si>
-    <t>A formal identifier that is used to identify this activity definition when it is represented in other formats, or referenced in a specification, model, design or an instance.</t>
-  </si>
-  <si>
-    <t>Typically, this is used for identifiers that can go in an HL7 V3 II (instance identifier) data type, and can then identify this activity definition outside of FHIR, where it is not possible to use the logical URI.</t>
-  </si>
-  <si>
-    <t>Allows externally provided and/or usable business identifiers to be easily associated with the module.</t>
-  </si>
-  <si>
-    <t>Definition.identifier</t>
-  </si>
-  <si>
-    <t>.identifier</t>
-  </si>
-  <si>
-    <t>no-gen-base</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.version</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Business version of the activity definition</t>
-  </si>
-  <si>
-    <t>The identifier that is used to identify this version of the activity definition when it is referenced in a specification, model, design or instance. This is an arbitrary value managed by the activity definition author and is not expected to be globally unique. For example, it might be a timestamp (e.g. yyyymmdd) if a managed version is not available. There is also no expectation that versions can be placed in a lexicographical sequence. To provide a version consistent with the Decision Support Service specification, use the format Major.Minor.Revision (e.g. 1.0.0). For more information on versioning knowledge assets, refer to the Decision Support Service specification. Note that a version is required for non-experimental active assets.</t>
-  </si>
-  <si>
-    <t>There may be different activity definition instances that have the same identifier but different versions.  The version can be appended to the url in a reference to allow a reference to a particular business version of the activity definition with the format [url]|[version].</t>
-  </si>
-  <si>
-    <t>Definition.version</t>
-  </si>
-  <si>
-    <t>N/A (to add?)</t>
-  </si>
-  <si>
-    <t>FiveWs.version</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.name</t>
-  </si>
-  <si>
-    <t>Name for this activity definition (computer friendly)</t>
-  </si>
-  <si>
-    <t>A natural language name identifying the activity definition. This name should be usable as an identifier for the module by machine processing applications such as code generation.</t>
-  </si>
-  <si>
-    <t>The name is not expected to be globally unique. The name should be a simple alphanumeric type name to ensure that it is machine-processing friendly.</t>
-  </si>
-  <si>
-    <t>Support human navigation and code generation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">inv-0
-</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.title</t>
-  </si>
-  <si>
-    <t>Name for this activity definition (human friendly)</t>
-  </si>
-  <si>
-    <t>A short, descriptive, user-friendly title for the activity definition.</t>
-  </si>
-  <si>
-    <t>This name does not need to be machine-processing friendly and may contain punctuation, white-space, etc.</t>
-  </si>
-  <si>
-    <t>Definition.title</t>
-  </si>
-  <si>
-    <t>.title</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.subtitle</t>
-  </si>
-  <si>
-    <t>Subordinate title of the activity definition</t>
-  </si>
-  <si>
-    <t>An explanatory or alternate title for the activity definition giving additional information about its content.</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.status</t>
-  </si>
-  <si>
-    <t>draft | active | retired | unknown</t>
-  </si>
-  <si>
-    <t>The status of this activity definition. Enables tracking the life-cycle of the content.</t>
-  </si>
-  <si>
-    <t>Allows filtering of activity definitions that are appropriate for use versus not.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>The lifecycle status of an artifact.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/publication-status|4.0.1</t>
-  </si>
-  <si>
-    <t>Definition.status {different ValueSet}</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.experimental</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>For testing purposes, not real usage</t>
-  </si>
-  <si>
-    <t>A Boolean value to indicate that this activity definition is authored for testing purposes (or education/evaluation/marketing) and is not intended to be used for genuine usage.</t>
-  </si>
-  <si>
-    <t>Enables experimental content to be developed following the same lifecycle that would be used for a production-level activity definition.</t>
-  </si>
-  <si>
-    <t>Definition.experimental</t>
-  </si>
-  <si>
-    <t>FiveWs.class</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.subject[x]</t>
-  </si>
-  <si>
-    <t>CodeableConcept
-Reference(Group)</t>
-  </si>
-  <si>
-    <t>Type of individual the activity definition is intended for</t>
-  </si>
-  <si>
-    <t>A code or group definition that describes the intended subject of the activity being defined.</t>
-  </si>
-  <si>
-    <t>Patient</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>The possible types of subjects for an activity (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
-  </si>
-  <si>
-    <t>Definition.subject</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revision Date
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
-  </si>
-  <si>
-    <t>Date last changed</t>
-  </si>
-  <si>
-    <t>The date  (and optionally time) when the activity definition was published. The date must change when the business version changes and it must change if the status code changes. In addition, it should change when the substantive content of the activity definition changes.</t>
-  </si>
-  <si>
-    <t>Note that this is not the same as the resource last-modified-date, since the resource may be a secondary representation of the activity definition. Additional specific dates may be added as extensions or be found by consulting Provenances associated with past versions of the resource.</t>
-  </si>
-  <si>
-    <t>Definition.date</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].time</t>
-  </si>
-  <si>
-    <t>FiveWs.recorded</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.publisher</t>
-  </si>
-  <si>
-    <t>Name of the publisher (organization or individual)</t>
-  </si>
-  <si>
-    <t>The name of the organization or individual that published the activity definition.</t>
-  </si>
-  <si>
-    <t>Usually an organization but may be an individual. The publisher (or steward) of the activity definition is the organization or individual primarily responsible for the maintenance and upkeep of the activity definition. This is not necessarily the same individual or organization that developed and initially authored the content. The publisher is the primary point of contact for questions or issues with the activity definition. This item SHOULD be populated unless the information is available from context.</t>
-  </si>
-  <si>
-    <t>Helps establish the "authority/credibility" of the activity definition.  May also allow for contact.</t>
-  </si>
-  <si>
-    <t>Definition.publisher {as string instead of CodeableConcept}</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT].role</t>
-  </si>
-  <si>
-    <t>FiveWs.witness</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.contact</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ContactDetail
-</t>
-  </si>
-  <si>
-    <t>Contact details for the publisher</t>
-  </si>
-  <si>
-    <t>Contact details to assist a user in finding and communicating with the publisher.</t>
-  </si>
-  <si>
-    <t>May be a web site, an email address, a telephone number, etc.</t>
-  </si>
-  <si>
-    <t>Definition.contact</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=CALLBCK].role</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">markdown
-</t>
-  </si>
-  <si>
-    <t>Natural language description of the activity definition</t>
-  </si>
-  <si>
-    <t>A free text natural language description of the activity definition from a consumer's perspective.</t>
-  </si>
-  <si>
-    <t>This description can be used to capture details such as why the activity definition was built, comments about misuse, instructions for clinical use and interpretation, literature references, examples from the paper world, etc. It is not a rendering of the activity definition as conveyed in the 'text' field of the resource itself. This item SHOULD be populated unless the information is available from context (e.g. the language of the activity definition is presumed to be the predominant language in the place the activity definition was created).</t>
-  </si>
-  <si>
-    <t>Definition.description</t>
-  </si>
-  <si>
-    <t>.text</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.useContext</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UsageContext
-</t>
-  </si>
-  <si>
-    <t>The context that the content is intended to support</t>
-  </si>
-  <si>
-    <t>The content was developed with a focus and intent of supporting the contexts that are listed. These contexts may be general categories (gender, age, ...) or may be references to specific programs (insurance plans, studies, ...) and may be used to assist with indexing and searching for appropriate activity definition instances.</t>
-  </si>
-  <si>
-    <t>When multiple useContexts are specified, there is no expectation that all or any of the contexts apply.</t>
-  </si>
-  <si>
-    <t>Assist in searching for appropriate content.</t>
-  </si>
-  <si>
-    <t>Definition.useContext</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.jurisdiction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Intended jurisdiction for activity definition (if applicable)</t>
-  </si>
-  <si>
-    <t>A legal or geographic region in which the activity definition is intended to be used.</t>
-  </si>
-  <si>
-    <t>It may be possible for the activity definition to be used in jurisdictions other than those for which it was originally designed or intended.</t>
-  </si>
-  <si>
-    <t>Countries and regions within which this artifact is targeted for use.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
-  </si>
-  <si>
-    <t>Definition.jurisdiction</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.purpose</t>
-  </si>
-  <si>
-    <t>Why this activity definition is defined</t>
-  </si>
-  <si>
-    <t>Explanation of why this activity definition is needed and why it has been designed as it has.</t>
-  </si>
-  <si>
-    <t>This element does not describe the usage of the activity definition. Instead, it provides traceability of ''why'' the resource is either needed or ''why'' it is defined as it is.  This may be used to point to source materials or specifications that drove the structure of this activity definition.</t>
-  </si>
-  <si>
-    <t>Definition.purpose</t>
-  </si>
-  <si>
-    <t>.reasonCode.text</t>
-  </si>
-  <si>
-    <t>FiveWs.why[x]</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.usage</t>
-  </si>
-  <si>
-    <t>Describes the clinical usage of the activity definition</t>
-  </si>
-  <si>
-    <t>A detailed description of how the activity definition is used from a clinical perspective.</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.copyright</t>
-  </si>
-  <si>
-    <t>License
-Restrictions</t>
-  </si>
-  <si>
-    <t>Use and/or publishing restrictions</t>
-  </si>
-  <si>
-    <t>A copyright statement relating to the activity definition and/or its contents. Copyright statements are generally legal restrictions on the use and publishing of the activity definition.</t>
-  </si>
-  <si>
-    <t>Consumers must be able to determine any legal restrictions on the use of the activity definition and/or its content.</t>
-  </si>
-  <si>
-    <t>Definition.copyright</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.approvalDate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">date
-</t>
-  </si>
-  <si>
-    <t>When the activity definition was approved by publisher</t>
-  </si>
-  <si>
-    <t>The date on which the resource content was approved by the publisher. Approval happens once when the content is officially approved for usage.</t>
-  </si>
-  <si>
-    <t>The 'date' element may be more recent than the approval date because of minor changes or editorial corrections.</t>
-  </si>
-  <si>
-    <t>Definition.approvalDate</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="SUBJ"].act[classCode=CACT;moodCode=EVN;code="approval"].effectiveTime</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.lastReviewDate</t>
-  </si>
-  <si>
-    <t>When the activity definition was last reviewed</t>
-  </si>
-  <si>
-    <t>The date on which the resource content was last reviewed. Review happens periodically after approval but does not change the original approval date.</t>
-  </si>
-  <si>
-    <t>If specified, this date follows the original approval date.</t>
-  </si>
-  <si>
-    <t>Gives a sense of how "current" the content is.  Resources that have not been reviewed in a long time may have a risk of being less appropriate/relevant.</t>
-  </si>
-  <si>
-    <t>Definition.lastReviewDate</t>
-  </si>
-  <si>
-    <t>.outboundRelationship[typeCode="SUBJ"; subsetCode="RECENT"].act[classCode=CACT;moodCode=EVN;code="review"].effectiveTime</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.effectivePeriod</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>When the activity definition is expected to be used</t>
-  </si>
-  <si>
-    <t>The period during which the activity definition content was or is planned to be in active use.</t>
-  </si>
-  <si>
-    <t>The effective period for a activity definition  determines when the content is applicable for usage and is independent of publication and review dates. For example, a measure intended to be used for the year 2016 might be published in 2015.</t>
-  </si>
-  <si>
-    <t>Allows establishing a transition before a resource comes into effect and also allows for a sunsetting  process when new versions of the activity definition are or are expected to be used instead.</t>
-  </si>
-  <si>
-    <t>Definition.effectivePeriod</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.topic</t>
-  </si>
-  <si>
-    <t>E.g. Education, Treatment, Assessment, etc.</t>
-  </si>
-  <si>
-    <t>Descriptive topics related to the content of the activity. Topics provide a high-level categorization of the activity that can be useful for filtering and searching.</t>
-  </si>
-  <si>
-    <t>Repositories must be able to determine how to categorize the activity definition so that it can be found by topical searches.</t>
-  </si>
-  <si>
-    <t>example</t>
-  </si>
-  <si>
-    <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.author</t>
-  </si>
-  <si>
-    <t>Who authored the content</t>
-  </si>
-  <si>
-    <t>An individiual or organization primarily involved in the creation and maintenance of the content.</t>
-  </si>
-  <si>
-    <t>.participation[typeCode=AUT]</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.editor</t>
-  </si>
-  <si>
-    <t>Who edited the content</t>
-  </si>
-  <si>
-    <t>An individual or organization primarily responsible for internal coherence of the content.</t>
-  </si>
-  <si>
-    <t>ActivityDefinition.editor.id</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -1011,7 +1094,7 @@
     <t>Additional content defined by implementations</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -1057,7 +1140,10 @@
     <t>Who reviewed the content</t>
   </si>
   <si>
-    <t>An individual or organization primarily responsible for review of some aspect of the content.</t>
+    <t>An individual or organization asserted by the publisher to be primarily responsible for review of some aspect of the content.</t>
+  </si>
+  <si>
+    <t>See guidance around (not) making local changes to elements [here](http://hl7.org/fhir/R5/canonicalresource.html#localization).</t>
   </si>
   <si>
     <t>.participation[typeCode=VRF] {not clear whether VRF best corresponds to reviewer or endorser}</t>
@@ -1081,7 +1167,7 @@
     <t>Who endorsed the content</t>
   </si>
   <si>
-    <t>An individual or organization responsible for officially endorsing the content for use in some setting.</t>
+    <t>An individual or organization asserted by the publisher to be responsible for officially endorsing the content for use in some setting.</t>
   </si>
   <si>
     <t>ActivityDefinition.endorser.id</t>
@@ -1103,7 +1189,7 @@
 </t>
   </si>
   <si>
-    <t>Additional documentation, citations, etc.</t>
+    <t>Additional documentation, citations, etc</t>
   </si>
   <si>
     <t>Related artifacts such as additional documentation, justification, or bibliographic references.</t>
@@ -1140,16 +1226,16 @@
     <t>Kind of resource</t>
   </si>
   <si>
-    <t>A description of the kind of resource the activity definition is representing. For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest. Typically, but not always, this is a Request resource.</t>
-  </si>
-  <si>
-    <t>May determine what types of extensions are permitted.</t>
+    <t>A description of the kind of resource the activity definition is representing. For example, a MedicationRequest, a ServiceRequest, or a CommunicationRequest.</t>
+  </si>
+  <si>
+    <t>The kind element may only specify Request resource types to facilitate considering user input as part of processing the result of any automated clinical reasoning processes. To support creation of event resources, such as Observations, RiskAssessments, and DetectedIssues, use a Task resource with the focus of the task set to the event resource to be created. Note that the kind of resource to be created may determine what types of extensions are permitted.</t>
   </si>
   <si>
     <t>The kind of activity the definition is describing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-resource-types|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-resource-types|5.0.0</t>
   </si>
   <si>
     <t>.classCode</t>
@@ -1171,6 +1257,9 @@
     <t>Allows profiles to be used to describe the types of activities that can be performed within a workflow, protocol, or order set.</t>
   </si>
   <si>
+    <t>.templateId</t>
+  </si>
+  <si>
     <t>ActivityDefinition.code</t>
   </si>
   <si>
@@ -1207,7 +1296,10 @@
     <t>Codes indicating the degree of authority/intentionality associated with a request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-intent|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-intent|5.0.0</t>
+  </si>
+  <si>
+    <t>.moodCode { of the realized Activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.priority</t>
@@ -1222,7 +1314,10 @@
     <t>Identifies the level of importance to be assigned to actioning the request.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/request-priority|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/request-priority|5.0.0</t>
+  </si>
+  <si>
+    <t>.priority { of the realized activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.doNotPerform</t>
@@ -1234,26 +1329,54 @@
     <t>Set this to true if the definition is to indicate that a particular activity should NOT be performed. If true, this element should be interpreted to reinforce a negative coding. For example NPO as a code with a doNotPerform of true would still indicate to NOT perform the action.</t>
   </si>
   <si>
-    <t>This element is not intended to be used to communicate a decision support response to cancel an order in progress. That should be done with the "remove" type of a PlanDefinition or RequestGroup.</t>
+    <t>This element is not intended to be used to communicate a decision support response to cancel an order in progress. That should be done with the "remove" type of a PlanDefinition or RequestOrchestration.</t>
+  </si>
+  <si>
+    <t>.negationInd { of the realized activity }</t>
   </si>
   <si>
     <t>ActivityDefinition.timing[x]</t>
   </si>
   <si>
     <t>Timing
-dateTimeAgePeriodRangeDuration</t>
+AgeRangeDuration</t>
   </si>
   <si>
     <t>When activity is to occur</t>
   </si>
   <si>
-    <t>The period, timing or frequency upon which the described activity is to occur.</t>
+    <t>The timing or frequency upon which the described activity is to occur.</t>
+  </si>
+  <si>
+    <t>The intent of the timing element is to provide timing when the action should be performed. As a definitional resource, this timing is interpreted as part of an apply operation so that the timing of the result actions in a CarePlan or RequestOrchestration, for example, would be specified by evaluating the timing definition in the context of the apply and setting the resulting timing on the appropriate elements of the target resource. If the timing is an Age, the activity is expected to be performed when the subject is the given Age. When the timing is a Duration, the activity is expected to be performed within the specified duration from the apply. When the timing is a Range, it may be a range of Ages or Durations, providing a range for the expected timing of the resulting activity. When the timing is a Timing, it is establishing a schedule for the timing of the resulting activity.</t>
   </si>
   <si>
     <t>Allows prompting for activities and detection of missed planned activities.</t>
   </si>
   <si>
     <t>.effectiveTime</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.asNeeded[x]</t>
+  </si>
+  <si>
+    <t>boolean
+CodeableConcept</t>
+  </si>
+  <si>
+    <t>Preconditions for service</t>
+  </si>
+  <si>
+    <t>If a CodeableConcept is present, it indicates the pre-condition for performing the service.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+  </si>
+  <si>
+    <t>boolean: precondition.negationInd (inversed - so negationInd = true means asNeeded=false CodeableConcept: precondition.observationEventCriterion[code="Assertion"].value</t>
   </si>
   <si>
     <t>ActivityDefinition.location</t>
@@ -1263,7 +1386,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">CodeableReference(Location)
 </t>
   </si>
   <si>
@@ -1314,7 +1437,7 @@
     <t>Extensions that cannot be ignored even if unrecognized</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and managable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1324,7 +1447,7 @@
     <t>ActivityDefinition.participant.type</t>
   </si>
   <si>
-    <t>patient | practitioner | related-person | device</t>
+    <t>careteam | device | group | healthcareservice | location | organization | patient | practitioner | practitionerrole | relatedperson</t>
   </si>
   <si>
     <t>The type of participant in the action.</t>
@@ -1333,16 +1456,36 @@
     <t>The type of participant in the activity.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-type|5.0.0</t>
   </si>
   <si>
     <t>.role.classCode</t>
   </si>
   <si>
+    <t>ActivityDefinition.participant.typeCanonical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">canonical(CapabilityStatement)
+</t>
+  </si>
+  <si>
+    <t>Who or what can participate</t>
+  </si>
+  <si>
+    <t>ActivityDefinition.participant.typeReference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(CareTeam|Device|DeviceDefinition|Endpoint|Group|HealthcareService|Location|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
+</t>
+  </si>
+  <si>
+    <t>When this element is a reference, it SHOULD be a reference to a definitional resource (for example, a location type, rather than a specific location).</t>
+  </si>
+  <si>
     <t>ActivityDefinition.participant.role</t>
   </si>
   <si>
-    <t>E.g. Nurse, Surgeon, Parent, etc.</t>
+    <t>E.g. Nurse, Surgeon, Parent, etc</t>
   </si>
   <si>
     <t>The role the participant should play in performing the described action.</t>
@@ -1351,16 +1494,28 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://terminology.hl7.org/ValueSet/action-participant-role</t>
   </si>
   <si>
     <t>.role.code</t>
   </si>
   <si>
+    <t>ActivityDefinition.participant.function</t>
+  </si>
+  <si>
+    <t>E.g. Author, Reviewer, Witness, etc</t>
+  </si>
+  <si>
+    <t>Indicates how the actor will be involved in the action - author, reviewer, witness, etc.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-function</t>
+  </si>
+  <si>
     <t>ActivityDefinition.product[x]</t>
   </si>
   <si>
-    <t>Reference(Medication|Substance)
+    <t>Reference(Medication|Ingredient|Substance|SubstanceDefinition)
 CodeableConcept</t>
   </si>
   <si>
@@ -1445,7 +1600,7 @@
     <t>ActivityDefinition.specimenRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(SpecimenDefinition)
+    <t xml:space="preserve">canonical(SpecimenDefinition)
 </t>
   </si>
   <si>
@@ -1461,7 +1616,7 @@
     <t>ActivityDefinition.observationRequirement</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ObservationDefinition)
+    <t xml:space="preserve">canonical(ObservationDefinition)
 </t>
   </si>
   <si>
@@ -1526,10 +1681,10 @@
     <t>The path to the element to be set dynamically</t>
   </si>
   <si>
-    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolveable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R4/fhirpath.html#simple) for full details).</t>
-  </si>
-  <si>
-    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R4/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
+    <t>The path to the element to be customized. This is the path on the resource that will hold the result of the calculation defined by the expression. The specified path SHALL be a FHIRPath resolvable on the specified target type of the ActivityDefinition, and SHALL consist only of identifiers, constant indexers, and a restricted subset of functions. The path is allowed to contain qualifiers (.) to traverse sub-elements, as well as indexers ([x]) to traverse multiple-cardinality sub-elements (see the [Simple FHIRPath Profile](http://hl7.org/fhir/R5/fhirpath.html#simple) for full details).</t>
+  </si>
+  <si>
+    <t>The path attribute contains a [Simple FHIRPath Subset](http://hl7.org/fhir/R5/fhirpath.html#simple) that allows path traversal, but not calculation.</t>
   </si>
   <si>
     <t>ActivityDefinition.dynamicValue.expression</t>
@@ -1694,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="15.703125" customWidth="true"/>
@@ -1781,77 +1936,85 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="B13" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>22</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
-      </c>
-      <c r="B15" t="s" s="2">
-        <v>26</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
+        <v>33</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>35</v>
       </c>
-      <c r="B20" t="s" s="2">
+      <c r="B21" t="s" s="2">
         <v>36</v>
       </c>
     </row>
@@ -1862,7 +2025,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN79"/>
+  <dimension ref="A1:AN85"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="47.60546875" customWidth="true" bestFit="true"/>
@@ -1875,7 +2038,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="82.80859375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="168.890625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1889,8 +2052,8 @@
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="93.40625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.90625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="125.1875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="54.6171875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
@@ -1901,8 +2064,8 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="56.328125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="133.84765625" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="163.4453125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="48.05859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -2134,7 +2297,7 @@
         <v>83</v>
       </c>
       <c r="AM2" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AN2" t="s" s="2">
         <v>77</v>
@@ -2142,10 +2305,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -2156,7 +2319,7 @@
         <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>77</v>
@@ -2165,19 +2328,19 @@
         <v>77</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -2227,13 +2390,13 @@
         <v>77</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>77</v>
@@ -2256,10 +2419,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -2270,7 +2433,7 @@
         <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>77</v>
@@ -2279,16 +2442,16 @@
         <v>77</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2339,19 +2502,19 @@
         <v>77</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>77</v>
@@ -2368,10 +2531,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2382,28 +2545,28 @@
         <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -2453,19 +2616,19 @@
         <v>77</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>77</v>
@@ -2482,10 +2645,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -2496,7 +2659,7 @@
         <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>77</v>
@@ -2508,16 +2671,16 @@
         <v>77</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -2543,13 +2706,13 @@
         <v>77</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -2567,19 +2730,19 @@
         <v>77</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>77</v>
@@ -2596,21 +2759,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>77</v>
@@ -2622,16 +2785,16 @@
         <v>77</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -2681,28 +2844,28 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI7" t="s" s="2">
-        <v>77</v>
+        <v>121</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>120</v>
+        <v>77</v>
       </c>
       <c r="AM7" t="s" s="2">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="AN7" t="s" s="2">
         <v>77</v>
@@ -2710,14 +2873,14 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -2736,16 +2899,16 @@
         <v>77</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2795,7 +2958,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -2804,7 +2967,7 @@
         <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AJ8" t="s" s="2">
         <v>77</v>
@@ -2813,10 +2976,10 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN8" t="s" s="2">
         <v>77</v>
@@ -2824,10 +2987,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2850,13 +3013,13 @@
         <v>77</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2895,17 +3058,17 @@
         <v>77</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -2917,7 +3080,7 @@
         <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>77</v>
@@ -2934,13 +3097,13 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>77</v>
@@ -2950,10 +3113,10 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>77</v>
@@ -2962,13 +3125,13 @@
         <v>77</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3019,7 +3182,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -3028,10 +3191,10 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>142</v>
+        <v>77</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>77</v>
@@ -3048,14 +3211,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -3068,25 +3231,25 @@
         <v>77</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J11" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3135,7 +3298,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3147,16 +3310,16 @@
         <v>77</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM11" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN11" t="s" s="2">
         <v>77</v>
@@ -3164,10 +3327,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3175,10 +3338,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>77</v>
@@ -3187,22 +3350,22 @@
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -3251,28 +3414,28 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>157</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3280,10 +3443,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3303,22 +3466,22 @@
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O13" t="s" s="2">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3367,7 +3530,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3379,27 +3542,27 @@
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3410,7 +3573,7 @@
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
@@ -3419,19 +3582,19 @@
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3481,28 +3644,28 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>77</v>
@@ -3510,10 +3673,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3524,7 +3687,7 @@
         <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>77</v>
@@ -3533,23 +3696,21 @@
         <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>179</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
@@ -3573,13 +3734,11 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y15" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="Y15" s="2"/>
       <c r="Z15" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3597,28 +3756,28 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>77</v>
+        <v>185</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>77</v>
@@ -3626,10 +3785,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3640,7 +3799,7 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>77</v>
@@ -3649,21 +3808,23 @@
         <v>77</v>
       </c>
       <c r="J16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="O16" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="O16" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
       </c>
@@ -3711,28 +3872,28 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>77</v>
+        <v>191</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>186</v>
+        <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -3740,10 +3901,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3754,7 +3915,7 @@
         <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>77</v>
@@ -3763,18 +3924,20 @@
         <v>77</v>
       </c>
       <c r="J17" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>189</v>
-      </c>
-      <c r="N17" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="N17" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3823,28 +3986,28 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>77</v>
@@ -3852,10 +4015,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3863,32 +4026,30 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I18" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -3913,13 +4074,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>195</v>
+        <v>77</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3937,28 +4098,28 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>197</v>
+        <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>199</v>
+        <v>177</v>
       </c>
       <c r="AN18" t="s" s="2">
         <v>77</v>
@@ -3966,10 +4127,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3977,35 +4138,33 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I19" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>201</v>
+        <v>106</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>204</v>
-      </c>
+        <v>205</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
       </c>
@@ -4029,13 +4188,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -4053,28 +4212,28 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>173</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -4082,10 +4241,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4096,7 +4255,7 @@
         <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>77</v>
@@ -4105,90 +4264,94 @@
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>210</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>215</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="R20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="R20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X20" t="s" s="2">
-        <v>212</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Z20" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="AA20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF20" t="s" s="2">
-        <v>207</v>
-      </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>77</v>
@@ -4196,48 +4359,50 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q21" s="2"/>
+      <c r="Q21" t="s" s="2">
+        <v>225</v>
+      </c>
       <c r="R21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4257,13 +4422,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>77</v>
+        <v>226</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>77</v>
+        <v>227</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -4281,28 +4446,28 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4310,46 +4475,44 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>77</v>
+        <v>231</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
@@ -4397,28 +4560,28 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>77</v>
@@ -4426,10 +4589,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4440,7 +4603,7 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>77</v>
@@ -4449,21 +4612,23 @@
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4511,28 +4676,28 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>246</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
@@ -4540,10 +4705,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4554,7 +4719,7 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>77</v>
@@ -4563,19 +4728,19 @@
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4625,28 +4790,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4654,10 +4819,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4668,7 +4833,7 @@
         <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>77</v>
@@ -4677,23 +4842,21 @@
         <v>77</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>252</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>77</v>
       </c>
@@ -4741,28 +4904,28 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4770,10 +4933,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4793,21 +4956,23 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="O26" s="2"/>
+        <v>265</v>
+      </c>
+      <c r="O26" t="s" s="2">
+        <v>266</v>
+      </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
       </c>
@@ -4831,13 +4996,13 @@
         <v>77</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>260</v>
+        <v>77</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>77</v>
@@ -4855,7 +5020,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4867,16 +5032,16 @@
         <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -4884,10 +5049,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4898,7 +5063,7 @@
         <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>77</v>
@@ -4907,19 +5072,19 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>241</v>
+        <v>269</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4945,13 +5110,13 @@
         <v>77</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>77</v>
+        <v>183</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>77</v>
+        <v>273</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>77</v>
+        <v>274</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>77</v>
@@ -4969,39 +5134,39 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>267</v>
+        <v>77</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>268</v>
+        <v>177</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5012,7 +5177,7 @@
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -5024,15 +5189,17 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>168</v>
+        <v>255</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>278</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>279</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -5081,50 +5248,50 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>77</v>
+        <v>280</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>173</v>
+        <v>281</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>273</v>
+        <v>77</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
@@ -5136,18 +5303,16 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="N29" s="2"/>
-      <c r="O29" t="s" s="2">
-        <v>276</v>
-      </c>
+      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -5195,53 +5360,53 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>77</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
@@ -5250,18 +5415,20 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O30" s="2"/>
+        <v>290</v>
+      </c>
+      <c r="O30" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5309,39 +5476,39 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>284</v>
+        <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5352,10 +5519,10 @@
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H31" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I31" t="s" s="2">
         <v>77</v>
@@ -5364,19 +5531,19 @@
         <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>279</v>
+        <v>171</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5425,39 +5592,39 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5468,32 +5635,30 @@
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>297</v>
-      </c>
+        <v>303</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5541,39 +5706,39 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>77</v>
+        <v>305</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5584,10 +5749,10 @@
         <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5596,17 +5761,19 @@
         <v>77</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N33" s="2"/>
+        <v>308</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>309</v>
+      </c>
       <c r="O33" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5631,13 +5798,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5655,39 +5822,39 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>77</v>
+        <v>311</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5698,7 +5865,7 @@
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>77</v>
@@ -5707,19 +5874,23 @@
         <v>77</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>234</v>
+        <v>314</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>318</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
       </c>
@@ -5767,39 +5938,39 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>77</v>
+        <v>319</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>309</v>
+        <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>77</v>
+        <v>169</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5813,7 +5984,7 @@
         <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>77</v>
@@ -5822,16 +5993,20 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>234</v>
+        <v>269</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+        <v>322</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="O35" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
       </c>
@@ -5855,13 +6030,13 @@
         <v>77</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>77</v>
+        <v>326</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>77</v>
+        <v>327</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>77</v>
@@ -5879,7 +6054,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5891,7 +6066,7 @@
         <v>77</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>77</v>
@@ -5900,7 +6075,7 @@
         <v>77</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>77</v>
+        <v>177</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>77</v>
@@ -5908,10 +6083,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5922,7 +6097,7 @@
         <v>78</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>77</v>
@@ -5934,13 +6109,13 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>168</v>
+        <v>248</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5991,28 +6166,28 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>77</v>
+        <v>331</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -6020,14 +6195,14 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
@@ -6037,7 +6212,7 @@
         <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>77</v>
@@ -6046,17 +6221,15 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>334</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6093,19 +6266,19 @@
         <v>77</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6117,16 +6290,16 @@
         <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>77</v>
+        <v>335</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6134,10 +6307,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>323</v>
+        <v>336</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6145,10 +6318,10 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -6157,20 +6330,18 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6219,19 +6390,19 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>77</v>
@@ -6240,7 +6411,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>77</v>
@@ -6248,14 +6419,14 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>328</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6271,18 +6442,20 @@
         <v>77</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6319,19 +6492,19 @@
         <v>77</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6343,7 +6516,7 @@
         <v>77</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>77</v>
@@ -6352,7 +6525,7 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>77</v>
@@ -6360,10 +6533,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>333</v>
+        <v>347</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6371,30 +6544,32 @@
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>334</v>
+        <v>348</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6443,25 +6618,25 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
@@ -6472,10 +6647,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6486,7 +6661,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>77</v>
@@ -6495,16 +6670,16 @@
         <v>77</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>168</v>
+        <v>353</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6555,25 +6730,25 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
@@ -6584,14 +6759,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>338</v>
+        <v>357</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6601,7 +6776,7 @@
         <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I42" t="s" s="2">
         <v>77</v>
@@ -6610,16 +6785,16 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>319</v>
+        <v>358</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6657,19 +6832,19 @@
         <v>77</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>322</v>
+        <v>357</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6681,16 +6856,16 @@
         <v>77</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>77</v>
@@ -6698,10 +6873,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>339</v>
+        <v>362</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6709,10 +6884,10 @@
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>77</v>
@@ -6721,20 +6896,18 @@
         <v>77</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>77</v>
@@ -6783,19 +6956,19 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>77</v>
@@ -6804,7 +6977,7 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -6812,14 +6985,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>340</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6835,18 +7008,20 @@
         <v>77</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6883,19 +7058,19 @@
         <v>77</v>
       </c>
       <c r="AB44" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6907,7 +7082,7 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6916,7 +7091,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6924,10 +7099,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>341</v>
+        <v>364</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6935,30 +7110,32 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>234</v>
+        <v>171</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>349</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -7007,25 +7184,25 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>336</v>
+        <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
@@ -7036,10 +7213,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>365</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7050,7 +7227,7 @@
         <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>77</v>
@@ -7059,16 +7236,16 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>168</v>
+        <v>353</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>314</v>
+        <v>354</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7119,25 +7296,25 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>316</v>
+        <v>356</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
@@ -7148,14 +7325,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>345</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7165,7 +7342,7 @@
         <v>79</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>77</v>
@@ -7174,16 +7351,16 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>130</v>
+        <v>248</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>319</v>
+        <v>367</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>320</v>
+        <v>368</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>147</v>
+        <v>360</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7221,19 +7398,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>321</v>
+        <v>77</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>134</v>
+        <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>322</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7245,16 +7422,16 @@
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7262,10 +7439,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>346</v>
+        <v>369</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7273,10 +7450,10 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7285,20 +7462,18 @@
         <v>77</v>
       </c>
       <c r="J48" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>168</v>
+        <v>88</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>324</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>326</v>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7347,19 +7522,19 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI48" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7368,7 +7543,7 @@
         <v>77</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>77</v>
@@ -7376,14 +7551,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>370</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7399,18 +7574,20 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7447,19 +7624,19 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>77</v>
+        <v>345</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7471,7 +7648,7 @@
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7480,7 +7657,7 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7488,10 +7665,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>348</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7499,10 +7676,10 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
@@ -7511,23 +7688,21 @@
         <v>77</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="M50" t="s" s="2">
         <v>349</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="M50" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>353</v>
-      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7575,25 +7750,25 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7604,10 +7779,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7627,16 +7802,16 @@
         <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7687,7 +7862,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7699,13 +7874,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7716,10 +7891,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7730,7 +7905,7 @@
         <v>78</v>
       </c>
       <c r="G52" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H52" t="s" s="2">
         <v>77</v>
@@ -7739,21 +7914,23 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>105</v>
+        <v>374</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>361</v>
+        <v>375</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>362</v>
+        <v>376</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="O52" s="2"/>
+        <v>377</v>
+      </c>
+      <c r="O52" t="s" s="2">
+        <v>378</v>
+      </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
       </c>
@@ -7777,13 +7954,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -7801,28 +7978,28 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>360</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH52" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>77</v>
+        <v>379</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7830,10 +8007,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7844,7 +8021,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>77</v>
@@ -7856,18 +8033,16 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>368</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>371</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -7915,19 +8090,19 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>367</v>
+        <v>380</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>77</v>
@@ -7936,7 +8111,7 @@
         <v>77</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7944,10 +8119,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7958,7 +8133,7 @@
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>77</v>
@@ -7967,23 +8142,21 @@
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>255</v>
+        <v>106</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>373</v>
+        <v>386</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8007,13 +8180,13 @@
         <v>77</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>303</v>
+        <v>110</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>77</v>
@@ -8031,28 +8204,28 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8060,10 +8233,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8074,7 +8247,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -8086,16 +8259,18 @@
         <v>77</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>105</v>
+        <v>393</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>381</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>382</v>
+        <v>395</v>
       </c>
       <c r="N55" s="2"/>
-      <c r="O55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
       </c>
@@ -8119,13 +8294,13 @@
         <v>77</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>383</v>
+        <v>77</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>77</v>
@@ -8143,19 +8318,19 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK55" t="s" s="2">
         <v>77</v>
@@ -8164,7 +8339,7 @@
         <v>77</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -8172,10 +8347,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8186,7 +8361,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8195,19 +8370,23 @@
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>105</v>
+        <v>269</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>386</v>
+        <v>399</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="N56" s="2"/>
-      <c r="O56" s="2"/>
+        <v>400</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>402</v>
+      </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
       </c>
@@ -8231,13 +8410,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>194</v>
+        <v>325</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>388</v>
+        <v>403</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>389</v>
+        <v>404</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8255,19 +8434,19 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>385</v>
+        <v>398</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>77</v>
@@ -8276,7 +8455,7 @@
         <v>77</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>405</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8284,10 +8463,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8298,29 +8477,27 @@
         <v>78</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I57" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J57" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>201</v>
+        <v>106</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8345,13 +8522,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>409</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8369,19 +8546,19 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>77</v>
@@ -8390,7 +8567,7 @@
         <v>77</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>77</v>
+        <v>411</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8398,10 +8575,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8412,7 +8589,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8424,18 +8601,16 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>106</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>396</v>
+        <v>413</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>397</v>
+        <v>414</v>
       </c>
       <c r="N58" s="2"/>
-      <c r="O58" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8459,13 +8634,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>77</v>
+        <v>416</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8483,28 +8658,28 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>394</v>
+        <v>412</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>77</v>
+        <v>417</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8512,46 +8687,44 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>401</v>
+        <v>77</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J59" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>402</v>
+        <v>212</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>403</v>
+        <v>419</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>404</v>
+        <v>420</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>421</v>
+      </c>
+      <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
         <v>77</v>
       </c>
@@ -8599,28 +8772,28 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>400</v>
+        <v>418</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>407</v>
+        <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>422</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8628,10 +8801,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8642,7 +8815,7 @@
         <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
@@ -8654,16 +8827,20 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
+        <v>426</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -8711,28 +8888,28 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>77</v>
+        <v>429</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8740,10 +8917,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>413</v>
+        <v>430</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8754,7 +8931,7 @@
         <v>78</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8763,16 +8940,16 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>168</v>
+        <v>431</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>314</v>
+        <v>432</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>315</v>
+        <v>433</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8799,13 +8976,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>77</v>
+        <v>434</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8823,28 +9000,28 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>316</v>
+        <v>430</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8852,21 +9029,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>414</v>
+        <v>437</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>144</v>
+        <v>438</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -8878,18 +9055,20 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>130</v>
+        <v>439</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>319</v>
+        <v>440</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>320</v>
+        <v>441</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O62" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="O62" t="s" s="2">
+        <v>443</v>
+      </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -8937,28 +9116,28 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>322</v>
+        <v>437</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>77</v>
+        <v>444</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8966,14 +9145,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>445</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8986,26 +9165,22 @@
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>130</v>
+        <v>446</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>417</v>
+        <v>447</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>148</v>
-      </c>
+        <v>448</v>
+      </c>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
       </c>
@@ -9053,7 +9228,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>419</v>
+        <v>445</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9065,16 +9240,16 @@
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9082,10 +9257,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9093,10 +9268,10 @@
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>77</v>
@@ -9108,13 +9283,13 @@
         <v>77</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>105</v>
+        <v>171</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>421</v>
+        <v>337</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>422</v>
+        <v>338</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -9141,13 +9316,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>423</v>
+        <v>77</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>424</v>
+        <v>77</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9165,28 +9340,28 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>420</v>
+        <v>339</v>
       </c>
       <c r="AG64" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>77</v>
+        <v>340</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>97</v>
+        <v>77</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>425</v>
+        <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -9194,21 +9369,21 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
@@ -9220,15 +9395,17 @@
         <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>255</v>
+        <v>133</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>427</v>
+        <v>343</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="N65" s="2"/>
+        <v>344</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9253,13 +9430,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>429</v>
+        <v>77</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>430</v>
+        <v>77</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9277,28 +9454,28 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>426</v>
+        <v>346</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>431</v>
+        <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>77</v>
+        <v>341</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9306,42 +9483,46 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>432</v>
+        <v>452</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
-        <v>77</v>
+        <v>453</v>
       </c>
       <c r="E66" s="2"/>
       <c r="F66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I66" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>433</v>
+        <v>133</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>434</v>
+        <v>454</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N66" s="2"/>
-      <c r="O66" s="2"/>
+        <v>455</v>
+      </c>
+      <c r="N66" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O66" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P66" t="s" s="2">
         <v>77</v>
       </c>
@@ -9365,13 +9546,13 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>436</v>
+        <v>77</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>437</v>
+        <v>77</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>77</v>
@@ -9389,28 +9570,28 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH66" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>97</v>
+        <v>139</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>438</v>
+        <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9418,21 +9599,21 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>440</v>
+        <v>77</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H67" t="s" s="2">
         <v>77</v>
@@ -9444,13 +9625,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>441</v>
+        <v>106</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>442</v>
+        <v>458</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>443</v>
+        <v>459</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9477,13 +9658,13 @@
         <v>77</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>77</v>
+        <v>110</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>77</v>
+        <v>460</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>77</v>
+        <v>461</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>77</v>
@@ -9501,28 +9682,28 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>439</v>
+        <v>457</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>444</v>
+        <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9530,10 +9711,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9544,7 +9725,7 @@
         <v>78</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>77</v>
@@ -9556,17 +9737,15 @@
         <v>77</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>446</v>
+        <v>464</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>447</v>
+        <v>465</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>449</v>
-      </c>
+        <v>459</v>
+      </c>
+      <c r="N68" s="2"/>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9615,28 +9794,28 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>445</v>
+        <v>463</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9644,10 +9823,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9658,7 +9837,7 @@
         <v>78</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>77</v>
@@ -9670,20 +9849,18 @@
         <v>77</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>255</v>
+        <v>467</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>455</v>
-      </c>
+        <v>468</v>
+      </c>
+      <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
       </c>
@@ -9707,13 +9884,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>456</v>
+        <v>77</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>457</v>
+        <v>77</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -9731,28 +9908,28 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>451</v>
+        <v>466</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>458</v>
+        <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>77</v>
+        <v>462</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9760,10 +9937,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9771,10 +9948,10 @@
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>77</v>
@@ -9786,18 +9963,16 @@
         <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>460</v>
+        <v>269</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="N70" s="2"/>
-      <c r="O70" t="s" s="2">
-        <v>463</v>
-      </c>
+      <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
         <v>77</v>
       </c>
@@ -9821,13 +9996,13 @@
         <v>77</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>77</v>
+        <v>472</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>77</v>
+        <v>473</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>77</v>
@@ -9845,19 +10020,19 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>459</v>
+        <v>469</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>77</v>
@@ -9866,7 +10041,7 @@
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>77</v>
+        <v>474</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9874,10 +10049,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9888,7 +10063,7 @@
         <v>78</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>77</v>
@@ -9900,18 +10075,16 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>465</v>
+        <v>269</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>466</v>
+        <v>476</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>467</v>
+        <v>477</v>
       </c>
       <c r="N71" s="2"/>
-      <c r="O71" t="s" s="2">
-        <v>468</v>
-      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>77</v>
       </c>
@@ -9935,13 +10108,11 @@
         <v>77</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y71" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>325</v>
+      </c>
+      <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>77</v>
+        <v>478</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>77</v>
@@ -9959,19 +10130,19 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>77</v>
@@ -9980,7 +10151,7 @@
         <v>77</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>77</v>
+        <v>474</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -9988,10 +10159,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10002,7 +10173,7 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>77</v>
@@ -10014,13 +10185,13 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>465</v>
+        <v>480</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10047,13 +10218,13 @@
         <v>77</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="Y72" t="s" s="2">
-        <v>77</v>
+        <v>483</v>
       </c>
       <c r="Z72" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>77</v>
@@ -10071,19 +10242,19 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>469</v>
+        <v>479</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>77</v>
@@ -10092,7 +10263,7 @@
         <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>77</v>
+        <v>485</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10100,21 +10271,21 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H73" t="s" s="2">
         <v>77</v>
@@ -10126,17 +10297,15 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>473</v>
+        <v>488</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>474</v>
+        <v>489</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>475</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>476</v>
-      </c>
+        <v>490</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10185,28 +10354,28 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>472</v>
+        <v>486</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10214,10 +10383,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10240,16 +10409,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>409</v>
+        <v>493</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>478</v>
+        <v>494</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>479</v>
+        <v>495</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>480</v>
+        <v>496</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10299,7 +10468,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>477</v>
+        <v>492</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10311,16 +10480,16 @@
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>77</v>
+        <v>497</v>
       </c>
       <c r="AN74" t="s" s="2">
         <v>77</v>
@@ -10328,10 +10497,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10342,7 +10511,7 @@
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -10354,16 +10523,20 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>168</v>
+        <v>269</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>314</v>
+        <v>499</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="O75" t="s" s="2">
+        <v>502</v>
+      </c>
       <c r="P75" t="s" s="2">
         <v>77</v>
       </c>
@@ -10387,13 +10560,13 @@
         <v>77</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>77</v>
+        <v>325</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>77</v>
+        <v>503</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>77</v>
@@ -10411,28 +10584,28 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>316</v>
+        <v>498</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>77</v>
+        <v>505</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>77</v>
@@ -10440,18 +10613,18 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>482</v>
+        <v>506</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>144</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="G76" t="s" s="2">
         <v>79</v>
@@ -10466,18 +10639,18 @@
         <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>130</v>
+        <v>507</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>319</v>
+        <v>508</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="N76" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>509</v>
+      </c>
+      <c r="N76" s="2"/>
+      <c r="O76" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -10525,7 +10698,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>322</v>
+        <v>506</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10537,16 +10710,16 @@
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -10554,14 +10727,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>483</v>
+        <v>511</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>416</v>
+        <v>77</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -10574,25 +10747,23 @@
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>130</v>
+        <v>512</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>417</v>
+        <v>513</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="N77" t="s" s="2">
-        <v>147</v>
-      </c>
+        <v>514</v>
+      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
-        <v>148</v>
+        <v>515</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
@@ -10641,7 +10812,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>419</v>
+        <v>511</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10653,16 +10824,16 @@
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>136</v>
+        <v>98</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM77" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN77" t="s" s="2">
         <v>77</v>
@@ -10670,10 +10841,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10681,10 +10852,10 @@
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>77</v>
@@ -10696,17 +10867,15 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>168</v>
+        <v>512</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>485</v>
+        <v>517</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>486</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>487</v>
-      </c>
+        <v>518</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10755,28 +10924,28 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>484</v>
+        <v>516</v>
       </c>
       <c r="AG78" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ78" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN78" t="s" s="2">
         <v>77</v>
@@ -10784,10 +10953,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10795,10 +10964,10 @@
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>77</v>
@@ -10810,16 +10979,16 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>489</v>
+        <v>520</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>490</v>
+        <v>521</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>491</v>
+        <v>522</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>492</v>
+        <v>523</v>
       </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
@@ -10869,35 +11038,719 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>488</v>
+        <v>519</v>
       </c>
       <c r="AG79" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AK79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>128</v>
+        <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>77</v>
+        <v>131</v>
       </c>
       <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="N80" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="O80" s="2"/>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>346</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>341</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="O84" s="2"/>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="O85" s="2"/>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AN85" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN79">
+  <autoFilter ref="A1:AN85">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10907,7 +11760,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI78">
+  <conditionalFormatting sqref="A2:AI84">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:02:34+00:00</t>
+    <t>2023-05-11T19:57:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T19:57:24+00:00</t>
+    <t>2023-05-11T20:42:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-11T20:42:55+00:00</t>
+    <t>2023-05-12T08:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T08:27:31+00:00</t>
+    <t>2023-05-12T10:53:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T10:53:52+00:00</t>
+    <t>2023-05-12T13:58:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
+++ b/branches/master/StructureDefinition-hiv-lab-task-activity.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-12T13:58:20+00:00</t>
+    <t>2023-05-23T09:20:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
